--- a/AAII_Financials/Yearly/GRBK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GRBK_YR_FIN.xlsx
@@ -732,13 +732,13 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2098500</v>
+        <v>2040000</v>
       </c>
       <c r="E8" s="3">
-        <v>2098900</v>
+        <v>2061500</v>
       </c>
       <c r="F8" s="3">
-        <v>1777700</v>
+        <v>1749300</v>
       </c>
       <c r="G8" s="3">
         <v>1757800</v>
@@ -783,13 +783,13 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1457700</v>
+        <v>1399200</v>
       </c>
       <c r="E9" s="3">
-        <v>1395400</v>
+        <v>1354300</v>
       </c>
       <c r="F9" s="3">
-        <v>1229500</v>
+        <v>1201100</v>
       </c>
       <c r="G9" s="3">
         <v>1234800</v>
@@ -837,7 +837,7 @@
         <v>640800</v>
       </c>
       <c r="E10" s="3">
-        <v>703500</v>
+        <v>707200</v>
       </c>
       <c r="F10" s="3">
         <v>548200</v>
@@ -1011,7 +1011,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="3">
-        <v>-10700</v>
+        <v>-7000</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1128,13 +1128,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1689000</v>
+        <v>1630600</v>
       </c>
       <c r="E17" s="3">
-        <v>1622000</v>
+        <v>1580800</v>
       </c>
       <c r="F17" s="3">
-        <v>1422500</v>
+        <v>1394100</v>
       </c>
       <c r="G17" s="3">
         <v>1398700</v>
@@ -1182,7 +1182,7 @@
         <v>409400</v>
       </c>
       <c r="E18" s="3">
-        <v>477000</v>
+        <v>480700</v>
       </c>
       <c r="F18" s="3">
         <v>355200</v>
@@ -1305,7 +1305,7 @@
         <v>443300</v>
       </c>
       <c r="E21" s="3">
-        <v>506000</v>
+        <v>509700</v>
       </c>
       <c r="F21" s="3">
         <v>394900</v>
@@ -2972,7 +2972,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2100</v>
+        <v>69000</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -3074,7 +3074,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>275000</v>
+        <v>341800</v>
       </c>
       <c r="E60" s="3">
         <v>206900</v>
@@ -3125,7 +3125,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>326800</v>
+        <v>259900</v>
       </c>
       <c r="E61" s="3">
         <v>344900</v>
